--- a/brain/library/internal/scorecard/Home Health Agency Software Scorecard April 2026.xlsx
+++ b/brain/library/internal/scorecard/Home Health Agency Software Scorecard April 2026.xlsx
@@ -837,7 +837,7 @@
     <row r="3">
       <c r="B3" s="61" t="inlineStr">
         <is>
-          <t>XX Initial Screen</t>
+          <t>Home Health Agency Software — Initial Screen</t>
         </is>
       </c>
     </row>
@@ -869,13 +869,21 @@
           <t>Margins</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>15%+ EBITDA margins required</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Vertical SaaS for home health typically 25-35% EBITDA at scale; PE-backed leaders (WellSky, Axxess) report 30%+.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -883,13 +891,21 @@
           <t>Recurring Revenue</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Existing recurring/contractual revenue or clear path to convert</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Per-seat/per-episode subscription model; 85-95% recurring revenue is industry standard.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -897,13 +913,21 @@
           <t>Industry Growth</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Growth rate above GDP (~3%+)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>US home health software market growing 8-12% CAGR through 2030, well above GDP. Demographic tailwind + CMS push to home.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -911,13 +935,21 @@
           <t>Growth TAM</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>$500M+ total addressable market (investor floor)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>US home health software TAM ~$4.5B (&gt;$500M floor). 11,000+ Medicare-certified agencies + 20k+ non-certified.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="62" t="inlineStr">
@@ -925,10 +957,19 @@
           <t>VERDICT</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PASS — all 4</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>All 4 must pass to proceed to Industry Scorecard</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Proceed to Industry Scorecard.</t>
         </is>
       </c>
     </row>
@@ -945,10 +986,19 @@
           <t>Number of independently owned acquisition candidates</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>50-100</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Determines sprint duration, not go/no-go</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Independently owned software vendors serving small-mid agencies (sub-$20M ARR, non-PE, non-top-5).</t>
         </is>
       </c>
     </row>
@@ -958,7 +1008,11 @@
           <t>Sprint duration estimate</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Focused sprint (20-50 range)</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>50+ = long sprint | 20-50 = focused | 10-20 = fast | &lt;10 = very fast</t>
@@ -1007,7 +1061,7 @@
     <row r="3" customFormat="1" s="28">
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>XX Industry Scorecard</t>
+          <t>Home Health Agency Software — Industry Scorecard</t>
         </is>
       </c>
       <c r="C3" s="30" t="n"/>
@@ -1028,7 +1082,7 @@
     <row r="5" ht="14.5" customHeight="1">
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>XX  Industry Scorecard</t>
+          <t>Home Health Agency Software — Industry Scorecard</t>
         </is>
       </c>
       <c r="C5" s="36" t="inlineStr">
@@ -1158,7 +1212,7 @@
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t>&gt;10% industry growth</t>
+          <t>8-12% CAGR = ~3x GDP. Aging demographics + shift from SNF to home care.</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1254,7 @@
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>Data 'manipulation' is a huge pain point</t>
+          <t>Low cloud penetration among sub-$10M agencies; PDGM/OASIS-E regulatory catalyst forces software upgrades.</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1290,11 @@
           <t>Mostly Headwinds</t>
         </is>
       </c>
-      <c r="J11" s="23" t="n"/>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>Tailwinds: aging pop, Medicare Advantage home-care expansion, value-based care, hospital-at-home.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="B12" s="19" t="inlineStr">
@@ -1251,7 +1309,7 @@
       </c>
       <c r="E12" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F12" s="21" t="n"/>
@@ -1272,7 +1330,7 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>Data 'manipulation' is a huge pain point</t>
+          <t>Regulatory-driven (PDGM 2020, OASIS-E 2023); agencies MUST upgrade billing/clinical compliance software.</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1365,7 @@
       </c>
       <c r="E14" s="48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F14" s="9" t="n"/>
@@ -1328,7 +1386,7 @@
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>~7 well-known players</t>
+          <t>~30-50 meaningful software vendors serving 11,000+ agencies. Hundreds including niche tools.</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1424,7 @@
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>Largest has ~35% of market</t>
+          <t>Top 5 vendors (WellSky, MatrixCare, Homecare Homebase, HHAeXchange, Axxess) hold ~45% share. Long tail remains.</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1480,7 @@
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
-          <t>~80%/~55% recurring/non-rec gross margin</t>
+          <t>Vertical SaaS gross margins 70-80% typical.</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1497,7 @@
       </c>
       <c r="E18" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F18" s="9" t="n"/>
@@ -1460,7 +1518,7 @@
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>Probably close to 30%</t>
+          <t>EBITDA margins 20-30% at scale; sub-scale vendors 10-20%.</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1535,7 @@
       </c>
       <c r="E19" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F19" s="21" t="n"/>
@@ -1498,7 +1556,7 @@
       </c>
       <c r="J19" s="24" t="inlineStr">
         <is>
-          <t>Probably close to 20%</t>
+          <t>ROTC 15-20% typical for vertical SaaS; accretive M&amp;A improves.</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1612,7 @@
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t>Outstanding customer feedback</t>
+          <t>Agencies cannot bill Medicare without PDGM-compliant software. Replacement = operational freeze.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1629,7 @@
       </c>
       <c r="E22" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F22" s="9" t="n"/>
@@ -1592,7 +1650,7 @@
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>Weaker value proposition</t>
+          <t>Clear: compliance + billing + clinical documentation. Measurable ROI via clean-claim rates, DSO reduction.</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1667,7 @@
       </c>
       <c r="E23" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F23" s="21" t="n"/>
@@ -1630,7 +1688,7 @@
       </c>
       <c r="J23" s="24" t="inlineStr">
         <is>
-          <t>Can be replaced w/effort</t>
+          <t>Very high switching costs — OASIS data history, staff retraining, 6-12 month implementations.</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1723,7 @@
       </c>
       <c r="E25" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F25" s="9" t="n"/>
@@ -1686,7 +1744,7 @@
       </c>
       <c r="J25" s="23" t="inlineStr">
         <is>
-          <t>High visibility</t>
+          <t>AI documentation/ambient scribe disrupting clinical workflows; winners unclear.</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1761,7 @@
       </c>
       <c r="E26" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F26" s="9" t="n"/>
@@ -1724,7 +1782,7 @@
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>Some risk and frequency</t>
+          <t>CMS rate cuts (2023, 2024) squeeze agency budgets, pressuring software pricing. High regulatory change frequency.</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1820,7 @@
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>Some liability risks</t>
+          <t>HIPAA/PHI exposure; cybersecurity insurance costs rising.</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1858,7 @@
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>Low cyclicality</t>
+          <t>Healthcare services non-cyclical; Medicare spend stable across cycles.</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1896,7 @@
       </c>
       <c r="J29" s="24" t="inlineStr">
         <is>
-          <t>Some resiliency to trends</t>
+          <t>Shift-to-home tailwind positive; AI disruption risk offsetting.</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1931,7 @@
       </c>
       <c r="E31" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F31" s="9" t="n"/>
@@ -1894,7 +1952,7 @@
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>No VC-backed companies (only PE-owned)</t>
+          <t>Some VC — Forcura, Axxess (PE-backed), Medalogix. Not frothy but well-funded incumbents.</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1990,7 @@
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>High competition</t>
+          <t>Top 5 aggressive: WellSky (TPG), Homecare Homebase (Hearst), HHAeXchange (Bain) all well-capitalized and rolling up.</t>
         </is>
       </c>
     </row>
@@ -1949,7 +2007,7 @@
       </c>
       <c r="E33" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F33" s="9" t="n"/>
@@ -1970,7 +2028,7 @@
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>No new entrants</t>
+          <t>New AI-native entrants (ambient documentation, predictive readmit) but compliance moat limits.</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2042,7 @@
       <c r="D34" s="56" t="n"/>
       <c r="E34" s="48" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F34" s="9" t="n"/>
@@ -2005,7 +2063,7 @@
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No meaningful supplier power (cloud infra is commodity).</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2080,7 @@
       </c>
       <c r="E35" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F35" s="9" t="n"/>
@@ -2043,7 +2101,7 @@
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>Some customer power</t>
+          <t>CMS rate squeeze forces agencies to pressure vendor pricing. Enterprise agencies have significant leverage.</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2139,7 @@
       </c>
       <c r="J36" s="24" t="inlineStr">
         <is>
-          <t>Some substitutes</t>
+          <t>EMR expansion (Epic, Cerner) into home health moderate substitute threat for enterprise; low for SMB.</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2195,7 @@
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>Moderate complexity</t>
+          <t>Moderate complexity: clinical workflows + billing rules + interoperability.</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2212,7 @@
       </c>
       <c r="E39" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F39" s="21" t="n"/>
@@ -2175,7 +2233,7 @@
       </c>
       <c r="J39" s="24" t="inlineStr">
         <is>
-          <t>Some actionable levers</t>
+          <t>Pricing power (per-seat to per-episode), cross-sell (RCM, analytics, ambient AI), M&amp;A of point tools.</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2268,7 @@
       </c>
       <c r="E41" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -2231,7 +2289,7 @@
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>Neutral impact</t>
+          <t>Net positive: enables aging-in-place, reduces hospital readmissions, extends independent living.</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2306,7 @@
       </c>
       <c r="E42" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F42" s="13" t="n"/>
@@ -2269,7 +2327,7 @@
       </c>
       <c r="J42" s="25" t="inlineStr">
         <is>
-          <t>Neutral externalities</t>
+          <t>Positive externalities: lower total cost of care vs SNF, better patient outcomes.</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2343,7 @@
       </c>
       <c r="D43" s="18" t="inlineStr">
         <is>
-          <t>Commentary: N/A</t>
+          <t>Home Health Agency Software — high criticality, strong tailwinds, moat via regulatory compliance; risks: CMS rate pressure, AI disruption, enterprise consolidation.</t>
         </is>
       </c>
       <c r="E43" s="18" t="n"/>
